--- a/ig/nr/3.0.1/StructureDefinition-mesures-observation-steps-by-day.xlsx
+++ b/ig/nr/3.0.1/StructureDefinition-mesures-observation-steps-by-day.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$108</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$107</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4183" uniqueCount="671">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4145" uniqueCount="669">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-26T08:11:02+00:00</t>
+    <t>2023-04-26T08:20:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -326,6 +326,10 @@
 </t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+</t>
+  </si>
+  <si>
     <t>N/A</t>
   </si>
   <si>
@@ -400,10 +404,6 @@
     <t>Meta.versionId</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-</t>
-  </si>
-  <si>
     <t>Observation.meta.lastUpdated</t>
   </si>
   <si>
@@ -456,14 +456,7 @@
     <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
   </si>
   <si>
-    <t xml:space="preserve">value:$this}
-</t>
-  </si>
-  <si>
     <t>Meta.profile</t>
-  </si>
-  <si>
-    <t>Observation.meta.profile:MesObservationStepsByDay</t>
   </si>
   <si>
     <t>Observation.meta.security</t>
@@ -2421,10 +2414,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP108"/>
+  <dimension ref="A1:AP107"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="50.5" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="49.3046875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="49.3046875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="27.03125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
@@ -2848,7 +2841,7 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G4" t="s" s="2">
         <v>88</v>
@@ -2932,7 +2925,7 @@
         <v>100</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>78</v>
@@ -2944,7 +2937,7 @@
         <v>78</v>
       </c>
       <c r="AN4" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AO4" t="s" s="2">
         <v>78</v>
@@ -2955,10 +2948,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2981,13 +2974,13 @@
         <v>78</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -3038,7 +3031,7 @@
         <v>78</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>76</v>
@@ -3062,7 +3055,7 @@
         <v>78</v>
       </c>
       <c r="AN5" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AO5" t="s" s="2">
         <v>78</v>
@@ -3073,14 +3066,14 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
@@ -3099,16 +3092,16 @@
         <v>78</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -3146,19 +3139,19 @@
         <v>78</v>
       </c>
       <c r="AB6" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AC6" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AD6" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>76</v>
@@ -3170,7 +3163,7 @@
         <v>100</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>78</v>
@@ -3182,7 +3175,7 @@
         <v>78</v>
       </c>
       <c r="AN6" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AO6" t="s" s="2">
         <v>78</v>
@@ -3193,10 +3186,10 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -3222,13 +3215,13 @@
         <v>90</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -3278,7 +3271,7 @@
         <v>78</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>76</v>
@@ -3290,7 +3283,7 @@
         <v>100</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>78</v>
@@ -3302,7 +3295,7 @@
         <v>78</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AO7" t="s" s="2">
         <v>78</v>
@@ -3410,7 +3403,7 @@
         <v>100</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>78</v>
@@ -3422,7 +3415,7 @@
         <v>78</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AO8" t="s" s="2">
         <v>78</v>
@@ -3530,7 +3523,7 @@
         <v>100</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>78</v>
@@ -3542,7 +3535,7 @@
         <v>78</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AO9" t="s" s="2">
         <v>78</v>
@@ -3564,7 +3557,7 @@
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G10" t="s" s="2">
         <v>77</v>
@@ -3626,17 +3619,19 @@
         <v>78</v>
       </c>
       <c r="AB10" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC10" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD10" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE10" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF10" t="s" s="2">
         <v>141</v>
-      </c>
-      <c r="AC10" s="2"/>
-      <c r="AD10" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE10" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AF10" t="s" s="2">
-        <v>142</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>76</v>
@@ -3648,7 +3643,7 @@
         <v>100</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>78</v>
@@ -3660,7 +3655,7 @@
         <v>78</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AO10" t="s" s="2">
         <v>78</v>
@@ -3671,26 +3666,24 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="C11" t="s" s="2">
-        <v>7</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>78</v>
@@ -3699,16 +3692,16 @@
         <v>89</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -3719,7 +3712,7 @@
         <v>78</v>
       </c>
       <c r="S11" t="s" s="2">
-        <v>3</v>
+        <v>78</v>
       </c>
       <c r="T11" t="s" s="2">
         <v>78</v>
@@ -3734,13 +3727,13 @@
         <v>78</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>78</v>
+        <v>147</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>78</v>
+        <v>148</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>78</v>
+        <v>149</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>78</v>
@@ -3758,7 +3751,7 @@
         <v>78</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>76</v>
@@ -3770,7 +3763,7 @@
         <v>100</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>78</v>
@@ -3779,10 +3772,10 @@
         <v>78</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>78</v>
+        <v>151</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>107</v>
+        <v>152</v>
       </c>
       <c r="AO11" t="s" s="2">
         <v>78</v>
@@ -3793,10 +3786,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3819,16 +3812,16 @@
         <v>89</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3854,13 +3847,13 @@
         <v>78</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>78</v>
@@ -3878,7 +3871,7 @@
         <v>78</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>76</v>
@@ -3890,7 +3883,7 @@
         <v>100</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>78</v>
@@ -3899,10 +3892,10 @@
         <v>78</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>78</v>
@@ -3913,10 +3906,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3927,28 +3920,28 @@
         <v>76</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J13" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3974,13 +3967,13 @@
         <v>78</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>160</v>
+        <v>78</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>161</v>
+        <v>78</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>78</v>
@@ -3998,19 +3991,19 @@
         <v>78</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>78</v>
@@ -4019,10 +4012,10 @@
         <v>78</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>153</v>
+        <v>78</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>154</v>
+        <v>108</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>78</v>
@@ -4033,10 +4026,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -4053,22 +4046,22 @@
         <v>78</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>132</v>
+        <v>167</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -4094,13 +4087,13 @@
         <v>78</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>78</v>
+        <v>171</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>78</v>
+        <v>172</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>78</v>
+        <v>173</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>78</v>
@@ -4118,7 +4111,7 @@
         <v>78</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>76</v>
@@ -4130,7 +4123,7 @@
         <v>100</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>78</v>
@@ -4142,7 +4135,7 @@
         <v>78</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>78</v>
@@ -4153,14 +4146,14 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>78</v>
+        <v>176</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -4179,16 +4172,16 @@
         <v>78</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -4214,13 +4207,13 @@
         <v>78</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>173</v>
+        <v>78</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>174</v>
+        <v>78</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>175</v>
+        <v>78</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>78</v>
@@ -4238,7 +4231,7 @@
         <v>78</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>76</v>
@@ -4250,7 +4243,7 @@
         <v>100</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>78</v>
@@ -4262,7 +4255,7 @@
         <v>78</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>107</v>
+        <v>182</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>78</v>
@@ -4273,21 +4266,21 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>78</v>
@@ -4299,16 +4292,16 @@
         <v>78</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4358,19 +4351,19 @@
         <v>78</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>124</v>
+        <v>78</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>78</v>
@@ -4382,7 +4375,7 @@
         <v>78</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>184</v>
+        <v>102</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>78</v>
@@ -4393,14 +4386,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>186</v>
+        <v>110</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -4419,16 +4412,16 @@
         <v>78</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>187</v>
+        <v>111</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>188</v>
+        <v>112</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>190</v>
+        <v>114</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4466,19 +4459,19 @@
         <v>78</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>76</v>
@@ -4487,10 +4480,10 @@
         <v>77</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>78</v>
@@ -4502,7 +4495,7 @@
         <v>78</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>78</v>
@@ -4513,21 +4506,23 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="C18" s="2"/>
+        <v>190</v>
+      </c>
+      <c r="C18" t="s" s="2">
+        <v>194</v>
+      </c>
       <c r="D18" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>78</v>
@@ -4539,17 +4534,15 @@
         <v>78</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>110</v>
+        <v>195</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>111</v>
+        <v>196</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>78</v>
@@ -4586,19 +4579,19 @@
         <v>78</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>76</v>
@@ -4610,7 +4603,7 @@
         <v>100</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>78</v>
@@ -4622,7 +4615,7 @@
         <v>78</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>78</v>
@@ -4633,13 +4626,13 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>78</v>
@@ -4661,13 +4654,13 @@
         <v>78</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4718,7 +4711,7 @@
         <v>78</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>76</v>
@@ -4730,7 +4723,7 @@
         <v>100</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>78</v>
@@ -4742,7 +4735,7 @@
         <v>78</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>78</v>
@@ -4753,44 +4746,46 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="C20" t="s" s="2">
-        <v>201</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>202</v>
+        <v>111</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="N20" s="2"/>
-      <c r="O20" s="2"/>
+        <v>205</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O20" t="s" s="2">
+        <v>206</v>
+      </c>
       <c r="P20" t="s" s="2">
         <v>78</v>
       </c>
@@ -4826,19 +4821,19 @@
         <v>78</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>76</v>
@@ -4850,7 +4845,7 @@
         <v>100</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>78</v>
@@ -4862,7 +4857,7 @@
         <v>78</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>78</v>
@@ -4873,14 +4868,14 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4893,25 +4888,23 @@
         <v>78</v>
       </c>
       <c r="I21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J21" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="J21" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="K21" t="s" s="2">
-        <v>110</v>
+        <v>209</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>78</v>
@@ -4948,19 +4941,19 @@
         <v>78</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>76</v>
@@ -4972,22 +4965,22 @@
         <v>100</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>78</v>
+        <v>213</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>78</v>
+        <v>214</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>101</v>
+        <v>215</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>78</v>
+        <v>216</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>78</v>
@@ -4995,14 +4988,14 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>78</v>
+        <v>218</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -5021,17 +5014,19 @@
         <v>89</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N22" s="2"/>
+        <v>221</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>222</v>
+      </c>
       <c r="O22" t="s" s="2">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>78</v>
@@ -5080,7 +5075,7 @@
         <v>78</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>76</v>
@@ -5092,22 +5087,22 @@
         <v>100</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>124</v>
+        <v>224</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>218</v>
+        <v>78</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>78</v>
@@ -5115,14 +5110,14 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -5141,20 +5136,18 @@
         <v>89</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>225</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>78</v>
       </c>
@@ -5202,7 +5195,7 @@
         <v>78</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>76</v>
@@ -5214,19 +5207,19 @@
         <v>100</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>78</v>
@@ -5237,44 +5230,46 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>231</v>
+        <v>78</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J24" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>232</v>
+        <v>167</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="O24" s="2"/>
+        <v>240</v>
+      </c>
+      <c r="O24" t="s" s="2">
+        <v>241</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>78</v>
       </c>
@@ -5298,13 +5293,13 @@
         <v>78</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>78</v>
+        <v>242</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>78</v>
+        <v>243</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>78</v>
+        <v>244</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>78</v>
@@ -5322,34 +5317,34 @@
         <v>78</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>226</v>
+        <v>101</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>78</v>
+        <v>246</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>78</v>
+        <v>249</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>78</v>
@@ -5357,10 +5352,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5371,31 +5366,31 @@
         <v>88</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>89</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>169</v>
+        <v>251</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>78</v>
@@ -5420,58 +5415,56 @@
         <v>78</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>244</v>
+        <v>171</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>246</v>
+        <v>257</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>258</v>
+      </c>
+      <c r="AC25" s="2"/>
       <c r="AD25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>247</v>
+        <v>78</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>248</v>
+        <v>78</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>78</v>
@@ -5479,12 +5472,14 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="C26" s="2"/>
+        <v>250</v>
+      </c>
+      <c r="C26" t="s" s="2">
+        <v>263</v>
+      </c>
       <c r="D26" t="s" s="2">
         <v>78</v>
       </c>
@@ -5493,7 +5488,7 @@
         <v>88</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>89</v>
@@ -5505,19 +5500,19 @@
         <v>78</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>78</v>
@@ -5542,29 +5537,31 @@
         <v>78</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="AC26" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>76</v>
@@ -5576,7 +5573,7 @@
         <v>100</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>78</v>
@@ -5585,13 +5582,13 @@
         <v>78</v>
       </c>
       <c r="AM26" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="AN26" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="AO26" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="AO26" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>78</v>
@@ -5602,23 +5599,21 @@
         <v>264</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="C27" t="s" s="2">
         <v>265</v>
       </c>
+      <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>78</v>
@@ -5627,20 +5622,16 @@
         <v>78</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>253</v>
+        <v>104</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>254</v>
+        <v>105</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>257</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>78</v>
       </c>
@@ -5664,13 +5655,13 @@
         <v>78</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>173</v>
+        <v>78</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>258</v>
+        <v>78</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>259</v>
+        <v>78</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>78</v>
@@ -5688,19 +5679,19 @@
         <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>252</v>
+        <v>107</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>124</v>
+        <v>78</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>78</v>
@@ -5709,13 +5700,13 @@
         <v>78</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>261</v>
+        <v>78</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>262</v>
+        <v>108</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>263</v>
+        <v>78</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>78</v>
@@ -5730,14 +5721,14 @@
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>78</v>
@@ -5749,15 +5740,17 @@
         <v>78</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>78</v>
@@ -5794,31 +5787,31 @@
         <v>78</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>78</v>
@@ -5830,7 +5823,7 @@
         <v>78</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>78</v>
@@ -5848,37 +5841,39 @@
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>110</v>
+        <v>143</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>111</v>
+        <v>270</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>112</v>
+        <v>271</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O29" s="2"/>
+        <v>272</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>273</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>78</v>
       </c>
@@ -5914,19 +5909,19 @@
         <v>78</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>117</v>
+        <v>274</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
@@ -5938,7 +5933,7 @@
         <v>100</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>78</v>
@@ -5947,10 +5942,10 @@
         <v>78</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>78</v>
+        <v>275</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>101</v>
+        <v>276</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>78</v>
@@ -5961,10 +5956,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5972,35 +5967,31 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G30" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="G30" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="H30" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>145</v>
+        <v>104</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>272</v>
+        <v>105</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>275</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>78</v>
       </c>
@@ -6048,19 +6039,19 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>276</v>
+        <v>107</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>124</v>
+        <v>78</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>78</v>
@@ -6069,10 +6060,10 @@
         <v>78</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>277</v>
+        <v>78</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>278</v>
+        <v>108</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>78</v>
@@ -6090,14 +6081,14 @@
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>78</v>
@@ -6109,15 +6100,17 @@
         <v>78</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N31" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>78</v>
@@ -6154,31 +6147,31 @@
         <v>78</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>78</v>
@@ -6190,7 +6183,7 @@
         <v>78</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>78</v>
@@ -6208,43 +6201,45 @@
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>111</v>
+        <v>283</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>112</v>
+        <v>284</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O32" s="2"/>
+        <v>285</v>
+      </c>
+      <c r="O32" t="s" s="2">
+        <v>286</v>
+      </c>
       <c r="P32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>78</v>
+        <v>287</v>
       </c>
       <c r="S32" t="s" s="2">
         <v>78</v>
@@ -6274,31 +6269,31 @@
         <v>78</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>117</v>
+        <v>288</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>78</v>
@@ -6307,10 +6302,10 @@
         <v>78</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>78</v>
+        <v>289</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>101</v>
+        <v>290</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>78</v>
@@ -6321,10 +6316,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6332,13 +6327,13 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>78</v>
@@ -6347,26 +6342,24 @@
         <v>89</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>132</v>
+        <v>104</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>288</v>
-      </c>
+        <v>295</v>
+      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
-        <v>289</v>
+        <v>78</v>
       </c>
       <c r="S33" t="s" s="2">
         <v>78</v>
@@ -6408,7 +6401,7 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>76</v>
@@ -6420,7 +6413,7 @@
         <v>100</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>78</v>
@@ -6429,10 +6422,10 @@
         <v>78</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>78</v>
@@ -6443,10 +6436,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6454,13 +6447,13 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>78</v>
@@ -6469,24 +6462,26 @@
         <v>89</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>103</v>
+        <v>167</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="O34" s="2"/>
+        <v>303</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>304</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>78</v>
+        <v>305</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>78</v>
@@ -6528,7 +6523,7 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>76</v>
@@ -6540,7 +6535,7 @@
         <v>100</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>78</v>
@@ -6549,10 +6544,10 @@
         <v>78</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>78</v>
@@ -6563,10 +6558,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6574,13 +6569,13 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>78</v>
@@ -6589,26 +6584,26 @@
         <v>89</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>169</v>
+        <v>104</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="N35" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="M35" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>305</v>
-      </c>
       <c r="O35" t="s" s="2">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>307</v>
+        <v>78</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>78</v>
@@ -6650,7 +6645,7 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>76</v>
@@ -6662,7 +6657,7 @@
         <v>100</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>78</v>
@@ -6671,10 +6666,10 @@
         <v>78</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>78</v>
@@ -6685,10 +6680,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6711,19 +6706,19 @@
         <v>89</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>103</v>
+        <v>319</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>305</v>
+        <v>322</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>78</v>
@@ -6772,7 +6767,7 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>76</v>
@@ -6784,7 +6779,7 @@
         <v>100</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>78</v>
@@ -6793,10 +6788,10 @@
         <v>78</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>78</v>
@@ -6807,10 +6802,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6833,19 +6828,19 @@
         <v>89</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>321</v>
+        <v>104</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>78</v>
@@ -6894,7 +6889,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
@@ -6906,7 +6901,7 @@
         <v>100</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>78</v>
@@ -6915,10 +6910,10 @@
         <v>78</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>78</v>
@@ -6929,24 +6924,24 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>78</v>
+        <v>337</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>78</v>
@@ -6955,19 +6950,19 @@
         <v>89</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>103</v>
+        <v>251</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>78</v>
@@ -6992,13 +6987,13 @@
         <v>78</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>78</v>
+        <v>147</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>78</v>
+        <v>342</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>78</v>
+        <v>343</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>78</v>
@@ -7016,10 +7011,10 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>88</v>
@@ -7028,69 +7023,65 @@
         <v>100</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>78</v>
+        <v>344</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>78</v>
+        <v>345</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>78</v>
+        <v>348</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>78</v>
+        <v>349</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>338</v>
+        <v>350</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>338</v>
+        <v>350</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>339</v>
+        <v>78</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>253</v>
+        <v>104</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>340</v>
+        <v>105</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>343</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>78</v>
       </c>
@@ -7114,13 +7105,13 @@
         <v>78</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>149</v>
+        <v>78</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>344</v>
+        <v>78</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>345</v>
+        <v>78</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>78</v>
@@ -7138,56 +7129,56 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>338</v>
+        <v>107</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>88</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>124</v>
+        <v>78</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>346</v>
+        <v>78</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>347</v>
+        <v>78</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>348</v>
+        <v>78</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>349</v>
+        <v>108</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>350</v>
+        <v>78</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>351</v>
+        <v>78</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>78</v>
@@ -7199,15 +7190,17 @@
         <v>78</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>78</v>
@@ -7244,31 +7237,31 @@
         <v>78</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>78</v>
@@ -7280,7 +7273,7 @@
         <v>78</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>78</v>
@@ -7291,14 +7284,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -7314,21 +7307,23 @@
         <v>78</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>110</v>
+        <v>143</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>111</v>
+        <v>270</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>112</v>
+        <v>271</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O41" s="2"/>
+        <v>272</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>273</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>78</v>
       </c>
@@ -7337,7 +7332,7 @@
         <v>78</v>
       </c>
       <c r="S41" t="s" s="2">
-        <v>78</v>
+        <v>353</v>
       </c>
       <c r="T41" t="s" s="2">
         <v>78</v>
@@ -7364,19 +7359,19 @@
         <v>78</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>117</v>
+        <v>274</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>76</v>
@@ -7388,7 +7383,7 @@
         <v>100</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>78</v>
@@ -7397,10 +7392,10 @@
         <v>78</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>78</v>
+        <v>275</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>101</v>
+        <v>276</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>78</v>
@@ -7425,7 +7420,7 @@
         <v>76</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>78</v>
@@ -7437,19 +7432,19 @@
         <v>89</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>145</v>
+        <v>104</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>272</v>
+        <v>329</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>273</v>
+        <v>330</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>274</v>
+        <v>331</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>275</v>
+        <v>332</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>78</v>
@@ -7459,7 +7454,7 @@
         <v>78</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>355</v>
+        <v>78</v>
       </c>
       <c r="T42" t="s" s="2">
         <v>78</v>
@@ -7498,19 +7493,19 @@
         <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>276</v>
+        <v>333</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>78</v>
@@ -7519,10 +7514,10 @@
         <v>78</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>277</v>
+        <v>334</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>278</v>
+        <v>335</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>78</v>
@@ -7533,10 +7528,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7544,13 +7539,13 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>78</v>
@@ -7559,19 +7554,19 @@
         <v>89</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>103</v>
+        <v>356</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>331</v>
+        <v>357</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>332</v>
+        <v>358</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>333</v>
+        <v>359</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>334</v>
+        <v>360</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>78</v>
@@ -7620,7 +7615,7 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>335</v>
+        <v>355</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>76</v>
@@ -7632,22 +7627,22 @@
         <v>100</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>124</v>
+        <v>224</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>78</v>
+        <v>361</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>336</v>
+        <v>362</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>337</v>
+        <v>363</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>78</v>
+        <v>364</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>78</v>
@@ -7655,10 +7650,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7666,13 +7661,13 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>78</v>
@@ -7681,20 +7676,18 @@
         <v>89</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>362</v>
-      </c>
+        <v>369</v>
+      </c>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>78</v>
       </c>
@@ -7742,34 +7735,34 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>363</v>
+        <v>78</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM44" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="AN44" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="AO44" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="AO44" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>78</v>
@@ -7777,21 +7770,21 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>78</v>
+        <v>372</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>78</v>
@@ -7803,18 +7796,20 @@
         <v>89</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="O45" s="2"/>
+        <v>376</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>377</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>78</v>
       </c>
@@ -7862,34 +7857,34 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>78</v>
+        <v>378</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>348</v>
+        <v>379</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>366</v>
+        <v>381</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>78</v>
@@ -7897,24 +7892,24 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>78</v>
@@ -7923,19 +7918,19 @@
         <v>89</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>376</v>
+        <v>385</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>377</v>
+        <v>386</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>78</v>
@@ -7984,7 +7979,7 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>76</v>
@@ -7993,25 +7988,25 @@
         <v>88</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>100</v>
+        <v>389</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>226</v>
+        <v>390</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>380</v>
+        <v>391</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>382</v>
+        <v>393</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>78</v>
@@ -8019,24 +8014,24 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>385</v>
+        <v>78</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>78</v>
@@ -8045,20 +8040,18 @@
         <v>89</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>386</v>
+        <v>126</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>387</v>
+        <v>396</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>390</v>
-      </c>
+        <v>398</v>
+      </c>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>78</v>
       </c>
@@ -8106,7 +8099,7 @@
         <v>78</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>76</v>
@@ -8115,25 +8108,25 @@
         <v>88</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>391</v>
+        <v>100</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>392</v>
+        <v>101</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>393</v>
+        <v>78</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>78</v>
@@ -8141,10 +8134,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8155,7 +8148,7 @@
         <v>76</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>78</v>
@@ -8167,18 +8160,20 @@
         <v>89</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>126</v>
+        <v>403</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="O48" s="2"/>
+        <v>222</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>406</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>78</v>
       </c>
@@ -8226,34 +8221,34 @@
         <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>124</v>
+        <v>224</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>78</v>
+        <v>407</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>78</v>
@@ -8261,10 +8256,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8275,10 +8270,10 @@
         <v>76</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>78</v>
@@ -8287,19 +8282,19 @@
         <v>89</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>224</v>
+        <v>414</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>78</v>
@@ -8336,59 +8331,59 @@
         <v>78</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC49" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>416</v>
+      </c>
+      <c r="AC49" s="2"/>
       <c r="AD49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>78</v>
+        <v>417</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>100</v>
+        <v>418</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>226</v>
+        <v>101</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>409</v>
+        <v>78</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>78</v>
+        <v>419</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>410</v>
+        <v>420</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>411</v>
+        <v>421</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>412</v>
+        <v>78</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>78</v>
+        <v>422</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>413</v>
+        <v>423</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="C50" s="2"/>
+        <v>411</v>
+      </c>
+      <c r="C50" t="s" s="2">
+        <v>424</v>
+      </c>
       <c r="D50" t="s" s="2">
         <v>78</v>
       </c>
@@ -8409,19 +8404,19 @@
         <v>89</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="N50" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="O50" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>78</v>
@@ -8431,7 +8426,7 @@
         <v>78</v>
       </c>
       <c r="S50" t="s" s="2">
-        <v>78</v>
+        <v>425</v>
       </c>
       <c r="T50" t="s" s="2">
         <v>78</v>
@@ -8458,17 +8453,19 @@
         <v>78</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="AC50" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>419</v>
+        <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>76</v>
@@ -8477,40 +8474,38 @@
         <v>88</v>
       </c>
       <c r="AI50" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AM50" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="AJ50" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="AK50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL50" t="s" s="2">
+      <c r="AN50" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="AM50" t="s" s="2">
+      <c r="AO50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AP50" t="s" s="2">
         <v>422</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="AO50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AP50" t="s" s="2">
-        <v>424</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="C51" t="s" s="2">
-        <v>426</v>
-      </c>
+        <v>427</v>
+      </c>
+      <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
         <v>78</v>
       </c>
@@ -8522,29 +8517,25 @@
         <v>88</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>414</v>
+        <v>104</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>415</v>
+        <v>105</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>417</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>78</v>
       </c>
@@ -8553,7 +8544,7 @@
         <v>78</v>
       </c>
       <c r="S51" t="s" s="2">
-        <v>427</v>
+        <v>78</v>
       </c>
       <c r="T51" t="s" s="2">
         <v>78</v>
@@ -8592,7 +8583,7 @@
         <v>78</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>413</v>
+        <v>107</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>76</v>
@@ -8601,28 +8592,28 @@
         <v>88</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>420</v>
+        <v>78</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>124</v>
+        <v>78</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>421</v>
+        <v>78</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>422</v>
+        <v>78</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>423</v>
+        <v>108</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>424</v>
+        <v>78</v>
       </c>
     </row>
     <row r="52" hidden="true">
@@ -8634,14 +8625,14 @@
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>78</v>
@@ -8653,15 +8644,17 @@
         <v>78</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N52" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>78</v>
@@ -8698,31 +8691,31 @@
         <v>78</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>78</v>
@@ -8734,7 +8727,7 @@
         <v>78</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>78</v>
@@ -8752,14 +8745,14 @@
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>78</v>
@@ -8768,21 +8761,23 @@
         <v>78</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>110</v>
+        <v>432</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>111</v>
+        <v>433</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>112</v>
+        <v>434</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O53" s="2"/>
+        <v>435</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>436</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>78</v>
       </c>
@@ -8818,31 +8813,31 @@
         <v>78</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>117</v>
+        <v>437</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>78</v>
@@ -8851,10 +8846,10 @@
         <v>78</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>78</v>
+        <v>438</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>101</v>
+        <v>439</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>78</v>
@@ -8865,10 +8860,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8885,30 +8880,32 @@
         <v>78</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J54" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>434</v>
+        <v>167</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>437</v>
+        <v>303</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q54" s="2"/>
+      <c r="Q54" t="s" s="2">
+        <v>445</v>
+      </c>
       <c r="R54" t="s" s="2">
         <v>78</v>
       </c>
@@ -8928,13 +8925,13 @@
         <v>78</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>78</v>
+        <v>242</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>78</v>
+        <v>446</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>78</v>
+        <v>447</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>78</v>
@@ -8952,7 +8949,7 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>439</v>
+        <v>448</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>76</v>
@@ -8964,7 +8961,7 @@
         <v>100</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>78</v>
@@ -8973,10 +8970,10 @@
         <v>78</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>440</v>
+        <v>449</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>441</v>
+        <v>450</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>78</v>
@@ -8987,10 +8984,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>442</v>
+        <v>451</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>443</v>
+        <v>452</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8998,7 +8995,7 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>88</v>
@@ -9007,37 +9004,35 @@
         <v>78</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J55" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>169</v>
+        <v>104</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>444</v>
+        <v>453</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>445</v>
+        <v>454</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>446</v>
+        <v>455</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q55" t="s" s="2">
-        <v>447</v>
-      </c>
+      <c r="Q55" s="2"/>
       <c r="R55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="S55" t="s" s="2">
-        <v>78</v>
+        <v>456</v>
       </c>
       <c r="T55" t="s" s="2">
         <v>78</v>
@@ -9052,13 +9047,13 @@
         <v>78</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>244</v>
+        <v>78</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>448</v>
+        <v>78</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>449</v>
+        <v>78</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>78</v>
@@ -9076,7 +9071,7 @@
         <v>78</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>450</v>
+        <v>457</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>76</v>
@@ -9088,7 +9083,7 @@
         <v>100</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>78</v>
@@ -9097,10 +9092,10 @@
         <v>78</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>78</v>
@@ -9111,10 +9106,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9137,19 +9132,19 @@
         <v>89</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>455</v>
+        <v>462</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>305</v>
+        <v>464</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>78</v>
@@ -9159,7 +9154,7 @@
         <v>78</v>
       </c>
       <c r="S56" t="s" s="2">
-        <v>458</v>
+        <v>78</v>
       </c>
       <c r="T56" t="s" s="2">
         <v>78</v>
@@ -9198,7 +9193,7 @@
         <v>78</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>76</v>
@@ -9207,10 +9202,10 @@
         <v>88</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>100</v>
+        <v>467</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>78</v>
@@ -9219,10 +9214,10 @@
         <v>78</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>461</v>
+        <v>468</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>78</v>
@@ -9233,10 +9228,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9259,19 +9254,19 @@
         <v>89</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>132</v>
+        <v>167</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>465</v>
+        <v>472</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>466</v>
+        <v>473</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>78</v>
@@ -9320,7 +9315,7 @@
         <v>78</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>76</v>
@@ -9329,10 +9324,10 @@
         <v>88</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>469</v>
+        <v>100</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>78</v>
@@ -9341,10 +9336,10 @@
         <v>78</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>78</v>
@@ -9355,10 +9350,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9366,34 +9361,34 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G58" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>169</v>
+        <v>251</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>78</v>
@@ -9418,13 +9413,13 @@
         <v>78</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>78</v>
+        <v>147</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>78</v>
+        <v>482</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>78</v>
+        <v>483</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>78</v>
@@ -9451,10 +9446,10 @@
         <v>88</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>100</v>
+        <v>484</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>78</v>
@@ -9463,10 +9458,10 @@
         <v>78</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>460</v>
+        <v>102</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>478</v>
+        <v>485</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>78</v>
@@ -9477,10 +9472,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>479</v>
+        <v>486</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>479</v>
+        <v>486</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9494,7 +9489,7 @@
         <v>88</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>78</v>
@@ -9503,20 +9498,16 @@
         <v>78</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>253</v>
+        <v>104</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>480</v>
+        <v>105</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>483</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>78</v>
       </c>
@@ -9540,13 +9531,13 @@
         <v>78</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>149</v>
+        <v>78</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>484</v>
+        <v>78</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>485</v>
+        <v>78</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>78</v>
@@ -9564,7 +9555,7 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>479</v>
+        <v>107</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>76</v>
@@ -9573,10 +9564,10 @@
         <v>88</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>486</v>
+        <v>78</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>124</v>
+        <v>78</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>78</v>
@@ -9585,10 +9576,10 @@
         <v>78</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>487</v>
+        <v>108</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>78</v>
@@ -9599,21 +9590,21 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>78</v>
@@ -9625,15 +9616,17 @@
         <v>78</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N60" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>78</v>
@@ -9670,31 +9663,31 @@
         <v>78</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC60" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>78</v>
@@ -9706,7 +9699,7 @@
         <v>78</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>78</v>
@@ -9717,14 +9710,14 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -9740,21 +9733,23 @@
         <v>78</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>110</v>
+        <v>143</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>111</v>
+        <v>270</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>112</v>
+        <v>271</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O61" s="2"/>
+        <v>272</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>273</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>78</v>
       </c>
@@ -9790,19 +9785,19 @@
         <v>78</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC61" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>117</v>
+        <v>274</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>76</v>
@@ -9814,7 +9809,7 @@
         <v>100</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>78</v>
@@ -9823,10 +9818,10 @@
         <v>78</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>78</v>
+        <v>275</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>101</v>
+        <v>276</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>78</v>
@@ -9837,10 +9832,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9851,7 +9846,7 @@
         <v>76</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>78</v>
@@ -9860,23 +9855,19 @@
         <v>78</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>145</v>
+        <v>104</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>272</v>
+        <v>105</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>275</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>78</v>
       </c>
@@ -9924,19 +9915,19 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>276</v>
+        <v>107</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>124</v>
+        <v>78</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>78</v>
@@ -9945,10 +9936,10 @@
         <v>78</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>277</v>
+        <v>78</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>278</v>
+        <v>108</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>78</v>
@@ -9959,21 +9950,21 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>78</v>
@@ -9985,15 +9976,17 @@
         <v>78</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N63" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>78</v>
@@ -10030,31 +10023,31 @@
         <v>78</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC63" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>78</v>
@@ -10066,7 +10059,7 @@
         <v>78</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>78</v>
@@ -10077,21 +10070,21 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>78</v>
@@ -10100,21 +10093,23 @@
         <v>78</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>111</v>
+        <v>283</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>112</v>
+        <v>284</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O64" s="2"/>
+        <v>285</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>286</v>
+      </c>
       <c r="P64" t="s" s="2">
         <v>78</v>
       </c>
@@ -10150,31 +10145,31 @@
         <v>78</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC64" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>117</v>
+        <v>288</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>78</v>
@@ -10183,10 +10178,10 @@
         <v>78</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>78</v>
+        <v>289</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>101</v>
+        <v>290</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>78</v>
@@ -10197,10 +10192,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10208,7 +10203,7 @@
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G65" t="s" s="2">
         <v>88</v>
@@ -10223,20 +10218,18 @@
         <v>89</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>132</v>
+        <v>104</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>288</v>
-      </c>
+        <v>295</v>
+      </c>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>78</v>
       </c>
@@ -10284,7 +10277,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>76</v>
@@ -10296,7 +10289,7 @@
         <v>100</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>78</v>
@@ -10305,10 +10298,10 @@
         <v>78</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>78</v>
@@ -10319,10 +10312,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10330,7 +10323,7 @@
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G66" t="s" s="2">
         <v>88</v>
@@ -10345,18 +10338,20 @@
         <v>89</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>103</v>
+        <v>167</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="O66" s="2"/>
+        <v>303</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>304</v>
+      </c>
       <c r="P66" t="s" s="2">
         <v>78</v>
       </c>
@@ -10404,7 +10399,7 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>76</v>
@@ -10416,7 +10411,7 @@
         <v>100</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>78</v>
@@ -10425,10 +10420,10 @@
         <v>78</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>78</v>
@@ -10439,10 +10434,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10450,7 +10445,7 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G67" t="s" s="2">
         <v>88</v>
@@ -10465,19 +10460,19 @@
         <v>89</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>169</v>
+        <v>104</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="N67" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="M67" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>305</v>
-      </c>
       <c r="O67" t="s" s="2">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>78</v>
@@ -10526,7 +10521,7 @@
         <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>76</v>
@@ -10538,7 +10533,7 @@
         <v>100</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>78</v>
@@ -10547,10 +10542,10 @@
         <v>78</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>78</v>
@@ -10561,10 +10556,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10587,19 +10582,19 @@
         <v>89</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>103</v>
+        <v>319</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>305</v>
+        <v>322</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>78</v>
@@ -10648,7 +10643,7 @@
         <v>78</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>76</v>
@@ -10660,7 +10655,7 @@
         <v>100</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>78</v>
@@ -10669,10 +10664,10 @@
         <v>78</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>78</v>
@@ -10683,10 +10678,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10709,19 +10704,19 @@
         <v>89</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>321</v>
+        <v>104</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>78</v>
@@ -10770,7 +10765,7 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>76</v>
@@ -10782,7 +10777,7 @@
         <v>100</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>78</v>
@@ -10791,10 +10786,10 @@
         <v>78</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>78</v>
@@ -10805,21 +10800,21 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>78</v>
+        <v>498</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>78</v>
@@ -10828,22 +10823,22 @@
         <v>78</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>103</v>
+        <v>251</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>331</v>
+        <v>499</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>332</v>
+        <v>500</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>333</v>
+        <v>501</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>334</v>
+        <v>502</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>78</v>
@@ -10868,13 +10863,13 @@
         <v>78</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>78</v>
+        <v>147</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>78</v>
+        <v>503</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>78</v>
+        <v>504</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>78</v>
@@ -10892,49 +10887,49 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>335</v>
+        <v>497</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>78</v>
+        <v>505</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>336</v>
+        <v>506</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>337</v>
+        <v>507</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>78</v>
+        <v>508</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>499</v>
+        <v>509</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>499</v>
+        <v>509</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>500</v>
+        <v>78</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -10953,19 +10948,19 @@
         <v>78</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>253</v>
+        <v>510</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>501</v>
+        <v>511</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>502</v>
+        <v>512</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>503</v>
+        <v>513</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>504</v>
+        <v>514</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>78</v>
@@ -10990,13 +10985,13 @@
         <v>78</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>149</v>
+        <v>78</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>505</v>
+        <v>78</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>506</v>
+        <v>78</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>78</v>
@@ -11014,7 +11009,7 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>499</v>
+        <v>509</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>76</v>
@@ -11026,33 +11021,33 @@
         <v>100</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>507</v>
+        <v>78</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>508</v>
+        <v>515</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>509</v>
+        <v>516</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>510</v>
+        <v>78</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11063,7 +11058,7 @@
         <v>76</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>78</v>
@@ -11075,20 +11070,18 @@
         <v>78</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>512</v>
+        <v>251</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>516</v>
-      </c>
+        <v>520</v>
+      </c>
+      <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>78</v>
       </c>
@@ -11112,13 +11105,13 @@
         <v>78</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>78</v>
+        <v>157</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>78</v>
+        <v>521</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>78</v>
+        <v>522</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>78</v>
@@ -11136,45 +11129,45 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>78</v>
+        <v>523</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>517</v>
+        <v>524</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>78</v>
+        <v>526</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11197,18 +11190,20 @@
         <v>78</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="O73" s="2"/>
+        <v>530</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>531</v>
+      </c>
       <c r="P73" t="s" s="2">
         <v>78</v>
       </c>
@@ -11232,13 +11227,13 @@
         <v>78</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>159</v>
+        <v>242</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>523</v>
+        <v>532</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>524</v>
+        <v>532</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>78</v>
@@ -11256,7 +11251,7 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>76</v>
@@ -11268,33 +11263,33 @@
         <v>100</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>525</v>
+        <v>78</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>526</v>
+        <v>533</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>528</v>
+        <v>78</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11317,20 +11312,16 @@
         <v>78</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>253</v>
+        <v>104</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>530</v>
+        <v>105</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>533</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N74" s="2"/>
+      <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>78</v>
       </c>
@@ -11354,13 +11345,13 @@
         <v>78</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>244</v>
+        <v>78</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>534</v>
+        <v>78</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>534</v>
+        <v>78</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>78</v>
@@ -11378,7 +11369,7 @@
         <v>78</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>529</v>
+        <v>107</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>76</v>
@@ -11387,10 +11378,10 @@
         <v>88</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>124</v>
+        <v>78</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>78</v>
@@ -11399,10 +11390,10 @@
         <v>78</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>535</v>
+        <v>78</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>536</v>
+        <v>108</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>78</v>
@@ -11413,21 +11404,21 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>78</v>
@@ -11439,15 +11430,17 @@
         <v>78</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N75" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>78</v>
@@ -11484,31 +11477,31 @@
         <v>78</v>
       </c>
       <c r="AB75" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC75" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD75" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>78</v>
@@ -11520,7 +11513,7 @@
         <v>78</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>78</v>
@@ -11531,14 +11524,14 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -11554,21 +11547,23 @@
         <v>78</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>110</v>
+        <v>143</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>111</v>
+        <v>270</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>112</v>
+        <v>271</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O76" s="2"/>
+        <v>272</v>
+      </c>
+      <c r="O76" t="s" s="2">
+        <v>273</v>
+      </c>
       <c r="P76" t="s" s="2">
         <v>78</v>
       </c>
@@ -11604,19 +11599,19 @@
         <v>78</v>
       </c>
       <c r="AB76" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC76" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>117</v>
+        <v>274</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>76</v>
@@ -11628,7 +11623,7 @@
         <v>100</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>78</v>
@@ -11637,10 +11632,10 @@
         <v>78</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>78</v>
+        <v>275</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>101</v>
+        <v>276</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>78</v>
@@ -11651,10 +11646,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11665,7 +11660,7 @@
         <v>76</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>78</v>
@@ -11674,23 +11669,19 @@
         <v>78</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>145</v>
+        <v>104</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>272</v>
+        <v>105</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>275</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N77" s="2"/>
+      <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>78</v>
       </c>
@@ -11738,19 +11729,19 @@
         <v>78</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>276</v>
+        <v>107</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>124</v>
+        <v>78</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>78</v>
@@ -11759,10 +11750,10 @@
         <v>78</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>277</v>
+        <v>78</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>278</v>
+        <v>108</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>78</v>
@@ -11773,21 +11764,21 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>78</v>
@@ -11799,15 +11790,17 @@
         <v>78</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N78" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>78</v>
@@ -11844,31 +11837,31 @@
         <v>78</v>
       </c>
       <c r="AB78" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC78" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD78" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE78" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>78</v>
@@ -11880,7 +11873,7 @@
         <v>78</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>78</v>
@@ -11891,21 +11884,21 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>78</v>
@@ -11914,21 +11907,23 @@
         <v>78</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>111</v>
+        <v>283</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>112</v>
+        <v>284</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O79" s="2"/>
+        <v>285</v>
+      </c>
+      <c r="O79" t="s" s="2">
+        <v>286</v>
+      </c>
       <c r="P79" t="s" s="2">
         <v>78</v>
       </c>
@@ -11964,31 +11959,31 @@
         <v>78</v>
       </c>
       <c r="AB79" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC79" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD79" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE79" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>117</v>
+        <v>288</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>78</v>
@@ -11997,10 +11992,10 @@
         <v>78</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>78</v>
+        <v>289</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>101</v>
+        <v>290</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>78</v>
@@ -12011,10 +12006,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12022,7 +12017,7 @@
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G80" t="s" s="2">
         <v>88</v>
@@ -12037,20 +12032,18 @@
         <v>89</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>132</v>
+        <v>104</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>288</v>
-      </c>
+        <v>295</v>
+      </c>
+      <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>78</v>
       </c>
@@ -12098,7 +12091,7 @@
         <v>78</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>76</v>
@@ -12110,7 +12103,7 @@
         <v>100</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>78</v>
@@ -12119,10 +12112,10 @@
         <v>78</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>78</v>
@@ -12133,10 +12126,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12144,7 +12137,7 @@
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G81" t="s" s="2">
         <v>88</v>
@@ -12159,18 +12152,20 @@
         <v>89</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>103</v>
+        <v>167</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="O81" s="2"/>
+        <v>303</v>
+      </c>
+      <c r="O81" t="s" s="2">
+        <v>304</v>
+      </c>
       <c r="P81" t="s" s="2">
         <v>78</v>
       </c>
@@ -12218,7 +12213,7 @@
         <v>78</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>76</v>
@@ -12230,7 +12225,7 @@
         <v>100</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>78</v>
@@ -12239,10 +12234,10 @@
         <v>78</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>78</v>
@@ -12253,10 +12248,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12264,7 +12259,7 @@
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G82" t="s" s="2">
         <v>88</v>
@@ -12279,19 +12274,19 @@
         <v>89</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>169</v>
+        <v>104</v>
       </c>
       <c r="L82" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="N82" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="M82" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>305</v>
-      </c>
       <c r="O82" t="s" s="2">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>78</v>
@@ -12340,7 +12335,7 @@
         <v>78</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>76</v>
@@ -12352,7 +12347,7 @@
         <v>100</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>78</v>
@@ -12361,10 +12356,10 @@
         <v>78</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>78</v>
@@ -12375,10 +12370,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12401,19 +12396,19 @@
         <v>89</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>103</v>
+        <v>319</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>305</v>
+        <v>322</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>78</v>
@@ -12462,7 +12457,7 @@
         <v>78</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>76</v>
@@ -12474,7 +12469,7 @@
         <v>100</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>78</v>
@@ -12483,10 +12478,10 @@
         <v>78</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>78</v>
@@ -12497,10 +12492,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12523,19 +12518,19 @@
         <v>89</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>321</v>
+        <v>104</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>78</v>
@@ -12584,7 +12579,7 @@
         <v>78</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>76</v>
@@ -12596,7 +12591,7 @@
         <v>100</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>78</v>
@@ -12605,10 +12600,10 @@
         <v>78</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>78</v>
@@ -12619,10 +12614,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12642,23 +12637,21 @@
         <v>78</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>103</v>
+        <v>547</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>331</v>
+        <v>548</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>332</v>
+        <v>549</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>334</v>
-      </c>
+        <v>550</v>
+      </c>
+      <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>78</v>
       </c>
@@ -12706,7 +12699,7 @@
         <v>78</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>335</v>
+        <v>546</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>76</v>
@@ -12718,33 +12711,33 @@
         <v>100</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>124</v>
+        <v>224</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>78</v>
+        <v>551</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>336</v>
+        <v>552</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>337</v>
+        <v>553</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AP85" t="s" s="2">
-        <v>78</v>
+        <v>554</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12767,16 +12760,16 @@
         <v>78</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>549</v>
+        <v>556</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>551</v>
+        <v>558</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>552</v>
+        <v>559</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -12826,7 +12819,7 @@
         <v>78</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>76</v>
@@ -12838,33 +12831,33 @@
         <v>100</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>553</v>
+        <v>560</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>554</v>
+        <v>561</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>555</v>
+        <v>562</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AP86" t="s" s="2">
-        <v>556</v>
+        <v>563</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>557</v>
+        <v>564</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>557</v>
+        <v>564</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12875,7 +12868,7 @@
         <v>76</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>78</v>
@@ -12887,18 +12880,20 @@
         <v>78</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>558</v>
+        <v>565</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>559</v>
+        <v>566</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>560</v>
+        <v>567</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="O87" s="2"/>
+        <v>568</v>
+      </c>
+      <c r="O87" t="s" s="2">
+        <v>569</v>
+      </c>
       <c r="P87" t="s" s="2">
         <v>78</v>
       </c>
@@ -12946,45 +12941,45 @@
         <v>78</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>557</v>
+        <v>564</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>226</v>
+        <v>570</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>562</v>
+        <v>78</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>563</v>
+        <v>571</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>564</v>
+        <v>572</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AP87" t="s" s="2">
-        <v>565</v>
+        <v>78</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>566</v>
+        <v>573</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>566</v>
+        <v>573</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12995,7 +12990,7 @@
         <v>76</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>78</v>
@@ -13007,20 +13002,16 @@
         <v>78</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>567</v>
+        <v>104</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>568</v>
+        <v>105</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>571</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N88" s="2"/>
+      <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>78</v>
       </c>
@@ -13068,19 +13059,19 @@
         <v>78</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>566</v>
+        <v>107</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>572</v>
+        <v>78</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>78</v>
@@ -13089,10 +13080,10 @@
         <v>78</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>573</v>
+        <v>78</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>574</v>
+        <v>108</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>78</v>
@@ -13103,21 +13094,21 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>78</v>
@@ -13129,15 +13120,17 @@
         <v>78</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N89" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>78</v>
@@ -13174,31 +13167,31 @@
         <v>78</v>
       </c>
       <c r="AB89" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC89" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD89" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE89" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>78</v>
@@ -13210,7 +13203,7 @@
         <v>78</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>78</v>
@@ -13221,14 +13214,14 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>109</v>
+        <v>576</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
@@ -13241,24 +13234,26 @@
         <v>78</v>
       </c>
       <c r="I90" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>111</v>
+        <v>577</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>112</v>
+        <v>578</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O90" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="O90" t="s" s="2">
+        <v>206</v>
+      </c>
       <c r="P90" t="s" s="2">
         <v>78</v>
       </c>
@@ -13294,19 +13289,19 @@
         <v>78</v>
       </c>
       <c r="AB90" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC90" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE90" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>117</v>
+        <v>579</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>76</v>
@@ -13318,7 +13313,7 @@
         <v>100</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>78</v>
@@ -13330,7 +13325,7 @@
         <v>78</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>78</v>
@@ -13341,46 +13336,44 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>578</v>
+        <v>78</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I91" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>110</v>
+        <v>581</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>208</v>
-      </c>
+        <v>584</v>
+      </c>
+      <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>78</v>
       </c>
@@ -13428,19 +13421,19 @@
         <v>78</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>100</v>
+        <v>585</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>118</v>
+        <v>586</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>78</v>
@@ -13449,10 +13442,10 @@
         <v>78</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>78</v>
+        <v>587</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>101</v>
+        <v>588</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>78</v>
@@ -13463,10 +13456,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>582</v>
+        <v>589</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>582</v>
+        <v>589</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13489,16 +13482,16 @@
         <v>78</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="L92" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="M92" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="N92" t="s" s="2">
         <v>584</v>
-      </c>
-      <c r="M92" t="s" s="2">
-        <v>585</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>586</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -13548,7 +13541,7 @@
         <v>78</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>582</v>
+        <v>589</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>76</v>
@@ -13557,22 +13550,22 @@
         <v>88</v>
       </c>
       <c r="AI92" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="AJ92" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="AK92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM92" t="s" s="2">
         <v>587</v>
       </c>
-      <c r="AJ92" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="AK92" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL92" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM92" t="s" s="2">
-        <v>589</v>
-      </c>
       <c r="AN92" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>78</v>
@@ -13583,10 +13576,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13609,18 +13602,20 @@
         <v>78</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>583</v>
+        <v>251</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="O93" s="2"/>
+        <v>596</v>
+      </c>
+      <c r="O93" t="s" s="2">
+        <v>597</v>
+      </c>
       <c r="P93" t="s" s="2">
         <v>78</v>
       </c>
@@ -13644,13 +13639,13 @@
         <v>78</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>78</v>
+        <v>171</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>78</v>
+        <v>598</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>78</v>
+        <v>599</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>78</v>
@@ -13668,7 +13663,7 @@
         <v>78</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>76</v>
@@ -13677,22 +13672,22 @@
         <v>88</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>587</v>
+        <v>100</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>588</v>
+        <v>101</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>78</v>
+        <v>600</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>589</v>
+        <v>601</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>594</v>
+        <v>507</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>78</v>
@@ -13703,10 +13698,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>595</v>
+        <v>602</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>595</v>
+        <v>602</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13717,7 +13712,7 @@
         <v>76</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>78</v>
@@ -13729,19 +13724,19 @@
         <v>78</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>596</v>
+        <v>603</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>597</v>
+        <v>604</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>598</v>
+        <v>605</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>599</v>
+        <v>606</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>78</v>
@@ -13766,13 +13761,13 @@
         <v>78</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>173</v>
+        <v>157</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>600</v>
+        <v>607</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>601</v>
+        <v>608</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>78</v>
@@ -13790,31 +13785,31 @@
         <v>78</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>595</v>
+        <v>602</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>78</v>
@@ -13825,10 +13820,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13839,7 +13834,7 @@
         <v>76</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>78</v>
@@ -13851,19 +13846,19 @@
         <v>78</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>253</v>
+        <v>610</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>605</v>
+        <v>611</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>606</v>
+        <v>612</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>607</v>
+        <v>613</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>608</v>
+        <v>614</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>78</v>
@@ -13888,55 +13883,55 @@
         <v>78</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="Y95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF95" t="s" s="2">
         <v>609</v>
       </c>
-      <c r="Z95" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="AA95" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB95" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC95" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD95" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE95" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF95" t="s" s="2">
-        <v>604</v>
-      </c>
       <c r="AG95" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>124</v>
+        <v>615</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>602</v>
+        <v>78</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>603</v>
+        <v>616</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>509</v>
+        <v>617</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>78</v>
@@ -13947,10 +13942,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>611</v>
+        <v>618</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>611</v>
+        <v>618</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13973,20 +13968,18 @@
         <v>78</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>612</v>
+        <v>104</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>613</v>
+        <v>619</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>615</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>616</v>
-      </c>
+        <v>303</v>
+      </c>
+      <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>78</v>
       </c>
@@ -14034,7 +14027,7 @@
         <v>78</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>611</v>
+        <v>618</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>76</v>
@@ -14046,7 +14039,7 @@
         <v>100</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>617</v>
+        <v>101</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>78</v>
@@ -14055,10 +14048,10 @@
         <v>78</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>618</v>
+        <v>587</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>78</v>
@@ -14069,10 +14062,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14083,7 +14076,7 @@
         <v>76</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>78</v>
@@ -14092,19 +14085,19 @@
         <v>78</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>103</v>
+        <v>623</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>305</v>
+        <v>626</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -14154,19 +14147,19 @@
         <v>78</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>124</v>
+        <v>224</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>78</v>
@@ -14175,10 +14168,10 @@
         <v>78</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>589</v>
+        <v>627</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>78</v>
@@ -14189,10 +14182,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14215,16 +14208,16 @@
         <v>89</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>627</v>
+        <v>632</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>628</v>
+        <v>633</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -14274,7 +14267,7 @@
         <v>78</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>76</v>
@@ -14286,7 +14279,7 @@
         <v>100</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>78</v>
@@ -14295,10 +14288,10 @@
         <v>78</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>78</v>
@@ -14309,10 +14302,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14326,7 +14319,7 @@
         <v>77</v>
       </c>
       <c r="H99" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I99" t="s" s="2">
         <v>78</v>
@@ -14335,18 +14328,20 @@
         <v>89</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>632</v>
+        <v>565</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>635</v>
-      </c>
-      <c r="O99" s="2"/>
+        <v>637</v>
+      </c>
+      <c r="O99" t="s" s="2">
+        <v>638</v>
+      </c>
       <c r="P99" t="s" s="2">
         <v>78</v>
       </c>
@@ -14394,7 +14389,7 @@
         <v>78</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>76</v>
@@ -14406,7 +14401,7 @@
         <v>100</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>226</v>
+        <v>639</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>78</v>
@@ -14415,10 +14410,10 @@
         <v>78</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>629</v>
+        <v>640</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>636</v>
+        <v>641</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>78</v>
@@ -14429,10 +14424,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14443,32 +14438,28 @@
         <v>76</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H100" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I100" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>567</v>
+        <v>104</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>638</v>
+        <v>105</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>638</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>639</v>
-      </c>
-      <c r="O100" t="s" s="2">
-        <v>640</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N100" s="2"/>
+      <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>78</v>
       </c>
@@ -14516,19 +14507,19 @@
         <v>78</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>637</v>
+        <v>107</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>641</v>
+        <v>78</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>78</v>
@@ -14537,10 +14528,10 @@
         <v>78</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>642</v>
+        <v>78</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>643</v>
+        <v>108</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>78</v>
@@ -14551,21 +14542,21 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>78</v>
@@ -14577,15 +14568,17 @@
         <v>78</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N101" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N101" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>78</v>
@@ -14622,31 +14615,31 @@
         <v>78</v>
       </c>
       <c r="AB101" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC101" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD101" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE101" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI101" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>78</v>
@@ -14658,7 +14651,7 @@
         <v>78</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>78</v>
@@ -14669,14 +14662,14 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>109</v>
+        <v>576</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
@@ -14689,24 +14682,26 @@
         <v>78</v>
       </c>
       <c r="I102" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>111</v>
+        <v>577</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>112</v>
+        <v>578</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O102" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="O102" t="s" s="2">
+        <v>206</v>
+      </c>
       <c r="P102" t="s" s="2">
         <v>78</v>
       </c>
@@ -14742,19 +14737,19 @@
         <v>78</v>
       </c>
       <c r="AB102" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC102" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD102" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE102" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>117</v>
+        <v>579</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>76</v>
@@ -14766,7 +14761,7 @@
         <v>100</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AK102" t="s" s="2">
         <v>78</v>
@@ -14778,7 +14773,7 @@
         <v>78</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>78</v>
@@ -14789,45 +14784,45 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>578</v>
+        <v>78</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H103" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I103" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J103" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>110</v>
+        <v>251</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>579</v>
+        <v>646</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>580</v>
+        <v>647</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>113</v>
+        <v>648</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>208</v>
+        <v>649</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>78</v>
@@ -14852,13 +14847,13 @@
         <v>78</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>78</v>
+        <v>147</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>78</v>
+        <v>342</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>78</v>
+        <v>343</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>78</v>
@@ -14876,34 +14871,34 @@
         <v>78</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>581</v>
+        <v>645</v>
       </c>
       <c r="AG103" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI103" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>78</v>
+        <v>650</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>78</v>
+        <v>346</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>101</v>
+        <v>347</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>78</v>
+        <v>348</v>
       </c>
       <c r="AP103" t="s" s="2">
         <v>78</v>
@@ -14911,10 +14906,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14922,7 +14917,7 @@
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G104" t="s" s="2">
         <v>88</v>
@@ -14937,19 +14932,19 @@
         <v>89</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>253</v>
+        <v>652</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>648</v>
+        <v>653</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>649</v>
+        <v>654</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>651</v>
+        <v>415</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>78</v>
@@ -14974,13 +14969,13 @@
         <v>78</v>
       </c>
       <c r="X104" t="s" s="2">
-        <v>149</v>
+        <v>242</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>344</v>
+        <v>656</v>
       </c>
       <c r="Z104" t="s" s="2">
-        <v>345</v>
+        <v>657</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>78</v>
@@ -14998,45 +14993,45 @@
         <v>78</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="AG104" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="AH104" t="s" s="2">
         <v>88</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>100</v>
+        <v>658</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>652</v>
+        <v>659</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>348</v>
+        <v>420</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>349</v>
+        <v>421</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>350</v>
+        <v>78</v>
       </c>
       <c r="AP104" t="s" s="2">
-        <v>78</v>
+        <v>422</v>
       </c>
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>653</v>
+        <v>660</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>653</v>
+        <v>660</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15056,22 +15051,22 @@
         <v>78</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>654</v>
+        <v>251</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>655</v>
+        <v>661</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>657</v>
+        <v>663</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>417</v>
+        <v>481</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>78</v>
@@ -15096,13 +15091,13 @@
         <v>78</v>
       </c>
       <c r="X105" t="s" s="2">
-        <v>244</v>
+        <v>147</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>658</v>
+        <v>482</v>
       </c>
       <c r="Z105" t="s" s="2">
-        <v>659</v>
+        <v>483</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>78</v>
@@ -15120,7 +15115,7 @@
         <v>78</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>653</v>
+        <v>660</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>76</v>
@@ -15129,50 +15124,50 @@
         <v>88</v>
       </c>
       <c r="AI105" t="s" s="2">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK105" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>661</v>
+        <v>78</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>422</v>
+        <v>102</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>423</v>
+        <v>485</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AP105" t="s" s="2">
-        <v>424</v>
+        <v>78</v>
       </c>
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>78</v>
+        <v>498</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H106" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I106" t="s" s="2">
         <v>78</v>
@@ -15181,19 +15176,19 @@
         <v>78</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>663</v>
+        <v>499</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>664</v>
+        <v>500</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>665</v>
+        <v>501</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>483</v>
+        <v>502</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>78</v>
@@ -15218,13 +15213,13 @@
         <v>78</v>
       </c>
       <c r="X106" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="Y106" t="s" s="2">
-        <v>484</v>
+        <v>503</v>
       </c>
       <c r="Z106" t="s" s="2">
-        <v>485</v>
+        <v>504</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>78</v>
@@ -15242,49 +15237,49 @@
         <v>78</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI106" t="s" s="2">
-        <v>666</v>
+        <v>100</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK106" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>78</v>
+        <v>505</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>101</v>
+        <v>506</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>487</v>
+        <v>507</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AP106" t="s" s="2">
-        <v>78</v>
+        <v>508</v>
       </c>
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
-        <v>500</v>
+        <v>78</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
@@ -15303,19 +15298,19 @@
         <v>78</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>253</v>
+        <v>79</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>501</v>
+        <v>667</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>502</v>
+        <v>668</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>503</v>
+        <v>568</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>504</v>
+        <v>569</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>78</v>
@@ -15340,13 +15335,13 @@
         <v>78</v>
       </c>
       <c r="X107" t="s" s="2">
-        <v>149</v>
+        <v>78</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>505</v>
+        <v>78</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>506</v>
+        <v>78</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>78</v>
@@ -15364,7 +15359,7 @@
         <v>78</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>76</v>
@@ -15373,154 +15368,32 @@
         <v>77</v>
       </c>
       <c r="AI107" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>124</v>
+        <v>78</v>
       </c>
       <c r="AK107" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>507</v>
+        <v>78</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>508</v>
+        <v>571</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>509</v>
+        <v>572</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AP107" t="s" s="2">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="108" hidden="true">
-      <c r="A108" t="s" s="2">
-        <v>668</v>
-      </c>
-      <c r="B108" t="s" s="2">
-        <v>668</v>
-      </c>
-      <c r="C108" s="2"/>
-      <c r="D108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E108" s="2"/>
-      <c r="F108" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G108" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K108" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="L108" t="s" s="2">
-        <v>669</v>
-      </c>
-      <c r="M108" t="s" s="2">
-        <v>670</v>
-      </c>
-      <c r="N108" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="O108" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="P108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q108" s="2"/>
-      <c r="R108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF108" t="s" s="2">
-        <v>668</v>
-      </c>
-      <c r="AG108" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH108" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM108" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="AN108" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="AO108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AP108" t="s" s="2">
         <v>78</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP108">
+  <autoFilter ref="A1:AP107">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -15530,7 +15403,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI107">
+  <conditionalFormatting sqref="A2:AI106">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
